--- a/モデリング/ダイヤ/ダイヤ.xlsx
+++ b/モデリング/ダイヤ/ダイヤ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wattz\Documents\BVE\日比谷線\モデリング\ダイヤ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wattz\Documents\BVE\日比谷線新\モデリング\ダイヤ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F2E8AA-32FE-4065-98CD-0733780FEEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38748A0B-289D-4258-BFF5-485616F491CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{CCDDCA3E-ED1C-4E77-8EA6-52E9521BDB8A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{CCDDCA3E-ED1C-4E77-8EA6-52E9521BDB8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="243">
   <si>
     <t>北千住</t>
     <rPh sb="0" eb="3">
@@ -882,10 +882,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>20003</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>11:00:00</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1264,6 +1260,52 @@
   </si>
   <si>
     <t>t</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダイヤの順番</t>
+    <rPh sb="4" eb="6">
+      <t>ジュンバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見直し</t>
+    <rPh sb="0" eb="2">
+      <t>ミナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2020/3/26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20007</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1333,8 +1375,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1350,7 +1392,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1646,7 +1688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B519C33-B239-41F0-B66D-795ED5BE4052}">
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="1" customWidth="1"/>
@@ -1796,19 +1838,19 @@
         <v>162</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB2" s="1" t="s">
         <v>161</v>
@@ -1864,19 +1906,19 @@
         <v>163</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U3" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="V3" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="W3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="Y3" s="1" t="s">
         <v>15</v>
@@ -1885,7 +1927,7 @@
         <v>163</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
@@ -1932,28 +1974,28 @@
         <v>133</v>
       </c>
       <c r="S4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="U4" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W4" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
@@ -2000,16 +2042,16 @@
         <v>134</v>
       </c>
       <c r="S5" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="T5" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="T5" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="W5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>15</v>
@@ -2071,19 +2113,19 @@
         <v>154</v>
       </c>
       <c r="S6" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="T6" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="V6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="W6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="X6" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>15</v>
@@ -2142,16 +2184,16 @@
         <v>155</v>
       </c>
       <c r="S7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="T7" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="T7" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="W7" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="X7" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>15</v>
@@ -2207,13 +2249,13 @@
         <v>111</v>
       </c>
       <c r="S8" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="T8" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="W8" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X8" s="1" t="s">
         <v>111</v>
@@ -2266,10 +2308,10 @@
         <v>140</v>
       </c>
       <c r="S9" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="T9" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>15</v>
@@ -2319,10 +2361,10 @@
         <v>141</v>
       </c>
       <c r="S10" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="T10" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>15</v>
@@ -2366,366 +2408,407 @@
         <v>111</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>111</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Z11" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
+      <c r="E13" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>39</v>
+        <v>236</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>71</v>
+        <v>237</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>71</v>
+        <v>235</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>158</v>
+        <v>234</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>172</v>
+        <v>76</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>74</v>
+        <v>143</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="Y14" s="1" t="s">
-        <v>211</v>
-      </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>9</v>
+        <v>170</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="1">
-        <v>13040</v>
+        <v>17</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>210</v>
+        <v>72</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>159</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>75</v>
+        <v>22</v>
+      </c>
+      <c r="G17" s="1">
+        <v>13040</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>50</v>
+        <v>165</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="1">
-        <v>6</v>
+        <v>40</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
+      </c>
+      <c r="G19" s="1">
+        <v>6</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>51</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>78</v>
+        <v>157</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>220</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="Q22" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="W22" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="M23" s="1" t="s">
+      <c r="U23" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="M24" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="Q24" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="W23" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="s">
+      <c r="W24" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M24" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="W24" s="1" t="s">
+      <c r="M25" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="B26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="W26" s="1" t="s">
         <v>181</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="B25" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="W25" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="W26" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.45">
       <c r="W27" s="1" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.45">
       <c r="W28" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="W29" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2744,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -2752,7 +2835,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -2816,12 +2899,12 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -2829,7 +2912,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -2837,10 +2920,10 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -2851,7 +2934,7 @@
         <v>165</v>
       </c>
       <c r="C14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
@@ -2862,7 +2945,7 @@
         <v>20003</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
@@ -2873,20 +2956,20 @@
         <v>13040</v>
       </c>
       <c r="C16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" t="s">
         <v>230</v>
-      </c>
-      <c r="B18" t="s">
-        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/モデリング/ダイヤ/ダイヤ.xlsx
+++ b/モデリング/ダイヤ/ダイヤ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wattz\Documents\BVE\日比谷線新\モデリング\ダイヤ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38748A0B-289D-4258-BFF5-485616F491CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55AB1A8-3558-4B9B-9782-CA1B2816746E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{CCDDCA3E-ED1C-4E77-8EA6-52E9521BDB8A}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="246">
   <si>
     <t>北千住</t>
     <rPh sb="0" eb="3">
@@ -291,14 +291,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>5:03</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1:38</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>4:00</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -819,10 +811,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>9:09:10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>70005</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1089,10 +1077,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>03-133</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>FreeRun</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1306,6 +1290,34 @@
   </si>
   <si>
     <t>20007</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03-108</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>13000</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9:10:10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9:14:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2:50</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1:40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5:11</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1338,12 +1350,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1363,7 +1381,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1371,6 +1389,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1688,21 +1709,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B519C33-B239-41F0-B66D-795ED5BE4052}">
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AD29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="1" customWidth="1"/>
     <col min="2" max="3" width="6.19921875" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.796875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.59765625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.69921875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.796875" style="1"/>
+    <col min="5" max="6" width="11.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.69921875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8.796875" style="1"/>
+    <col min="12" max="12" width="8.796875" style="3"/>
+    <col min="13" max="13" width="8.796875" style="1"/>
+    <col min="14" max="14" width="8.796875" style="3"/>
+    <col min="15" max="15" width="8.796875" style="1"/>
+    <col min="16" max="16" width="8.796875" style="3"/>
+    <col min="17" max="17" width="8.796875" style="1"/>
+    <col min="18" max="18" width="8.796875" style="3"/>
+    <col min="19" max="19" width="8.796875" style="1"/>
+    <col min="20" max="20" width="8.796875" style="3"/>
+    <col min="21" max="21" width="8.796875" style="1"/>
+    <col min="22" max="22" width="8.796875" style="3"/>
+    <col min="23" max="23" width="8.796875" style="1"/>
+    <col min="24" max="24" width="8.796875" style="3"/>
+    <col min="25" max="25" width="8.796875" style="1"/>
+    <col min="26" max="26" width="8.796875" style="3"/>
+    <col min="27" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1719,76 +1756,79 @@
         <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>45</v>
+      <c r="H1" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1804,62 +1844,71 @@
       <c r="E2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>68</v>
+      <c r="L2" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>130</v>
+        <v>80</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
+        <v>158</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1873,64 +1922,73 @@
         <v>7650</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>97</v>
+      <c r="H3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>114</v>
+        <v>95</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="O3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>132</v>
+      <c r="Q3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>189</v>
+        <v>241</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>206</v>
+        <v>186</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>174</v>
+        <v>203</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="Y3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AB3" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="AC3" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
+        <v>160</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1944,61 +2002,70 @@
         <v>8400</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>99</v>
+      <c r="H4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>116</v>
+        <v>97</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>133</v>
+      <c r="Q4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>191</v>
+        <v>109</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="Y4" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AB4" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="AC4" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
+        <v>188</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -2015,49 +2082,52 @@
         <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>101</v>
+      <c r="H5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>118</v>
+        <v>99</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>179</v>
+      <c r="Q5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="Y5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -2074,64 +2144,61 @@
         <v>33</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>48</v>
+        <v>245</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>103</v>
+        <v>53</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>120</v>
+        <v>101</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>136</v>
+        <v>118</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>133</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>111</v>
+        <v>134</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>185</v>
+        <v>109</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="Y6" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z6" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -2148,58 +2215,55 @@
         <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>105</v>
+        <v>55</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>122</v>
+        <v>103</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="O7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="P7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="Q7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -2216,55 +2280,52 @@
         <v>34</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>59</v>
+        <v>34</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>107</v>
+        <v>57</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>124</v>
+        <v>105</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="O8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>111</v>
+      <c r="T8" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="Y8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -2281,43 +2342,46 @@
         <v>36</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>61</v>
+      <c r="J9" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>109</v>
+        <v>59</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="O9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z9" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -2334,45 +2398,48 @@
         <v>37</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>65</v>
+      <c r="J10" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>111</v>
+        <v>63</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>128</v>
+        <v>109</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="O10" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="Z10" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1">
         <v>7245</v>
@@ -2387,428 +2454,434 @@
         <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>111</v>
+        <v>38</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z11" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.45">
       <c r="E13" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z13" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="L14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y15" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="L15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W16" s="1" t="s">
+      <c r="L16" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X16" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="3">
         <v>13040</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z17" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="H18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="3">
         <v>6</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="J19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="J20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="H21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y22" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="H22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="M24" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="W24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.45">
+      <c r="N24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="X25" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="W25" s="1" t="s">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.45">
+      <c r="B26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.45">
+      <c r="X27" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.45">
+      <c r="X28" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.45">
+      <c r="X29" s="3" t="s">
         <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="B26" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="W27" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="W28" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="W29" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2827,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -2835,7 +2908,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -2843,7 +2916,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -2875,7 +2948,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -2899,12 +2972,12 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -2912,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -2920,10 +2993,10 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -2931,10 +3004,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
@@ -2945,7 +3018,7 @@
         <v>20003</v>
       </c>
       <c r="C15" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
@@ -2956,20 +3029,20 @@
         <v>13040</v>
       </c>
       <c r="C16" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
